--- a/Backtest/02-10-23/S&P500stock_02-10-23period252RS90.xlsx
+++ b/Backtest/02-10-23/S&P500stock_02-10-23period252RS90.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="45">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="65" uniqueCount="62">
   <si>
     <t>Stock</t>
   </si>
@@ -127,28 +127,79 @@
     <t>EM Rating</t>
   </si>
   <si>
-    <t>HAL</t>
-  </si>
-  <si>
-    <t>ANET</t>
-  </si>
-  <si>
-    <t>2023-10-24</t>
-  </si>
-  <si>
-    <t>2023-10-30</t>
+    <t>XOM</t>
+  </si>
+  <si>
+    <t>SLB</t>
+  </si>
+  <si>
+    <t>URI</t>
+  </si>
+  <si>
+    <t>DECK</t>
+  </si>
+  <si>
+    <t>ON</t>
+  </si>
+  <si>
+    <t>GWW</t>
+  </si>
+  <si>
+    <t>JBL</t>
+  </si>
+  <si>
+    <t>2023-04-28</t>
+  </si>
+  <si>
+    <t>2023-04-21</t>
+  </si>
+  <si>
+    <t>2023-04-26</t>
+  </si>
+  <si>
+    <t>2023-05-25</t>
+  </si>
+  <si>
+    <t>2023-05-01</t>
+  </si>
+  <si>
+    <t>2023-04-27</t>
+  </si>
+  <si>
+    <t>2023-03-16</t>
   </si>
   <si>
     <t>Energy</t>
   </si>
   <si>
+    <t>Industrials</t>
+  </si>
+  <si>
+    <t>Consumer Cyclical</t>
+  </si>
+  <si>
     <t>Technology</t>
   </si>
   <si>
+    <t>Oil &amp; Gas Integrated</t>
+  </si>
+  <si>
     <t>Oil &amp; Gas Equipment &amp; Services</t>
   </si>
   <si>
-    <t>Computer Hardware</t>
+    <t>Rental &amp; Leasing Services</t>
+  </si>
+  <si>
+    <t>Footwear &amp; Accessories</t>
+  </si>
+  <si>
+    <t>Semiconductors</t>
+  </si>
+  <si>
+    <t>Industrial Distribution</t>
+  </si>
+  <si>
+    <t>Electronic Components</t>
   </si>
 </sst>
 </file>
@@ -506,7 +557,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AK3"/>
+  <dimension ref="A1:AK8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:37">
@@ -627,37 +678,37 @@
         <v>37</v>
       </c>
       <c r="B2">
-        <v>95.58232931726907</v>
+        <v>96.98795180722891</v>
       </c>
       <c r="C2">
-        <v>85</v>
+        <v>26</v>
       </c>
       <c r="D2">
-        <v>40.5</v>
+        <v>114.35</v>
       </c>
       <c r="E2">
-        <v>1.68</v>
+        <v>1.77</v>
       </c>
       <c r="F2">
-        <v>0.7071067811865475</v>
+        <v>-0.4850875587323145</v>
       </c>
       <c r="G2">
-        <v>1.8</v>
+        <v>1.62</v>
       </c>
       <c r="H2">
-        <v>-0.7071067811865476</v>
+        <v>-1.21526982610006</v>
       </c>
       <c r="I2">
-        <v>41.21800003051758</v>
+        <v>113.3679992675781</v>
       </c>
       <c r="J2">
-        <v>41.32450027465821</v>
+        <v>113.5014999389648</v>
       </c>
       <c r="K2">
-        <v>39.94720016479492</v>
+        <v>110.0079997253418</v>
       </c>
       <c r="L2">
-        <v>36.06554999351501</v>
+        <v>99.25489974975586</v>
       </c>
       <c r="M2">
         <v>1</v>
@@ -666,11 +717,11 @@
         <v>1.03</v>
       </c>
       <c r="P2">
+        <v>0</v>
+      </c>
+      <c r="Q2">
         <v>1</v>
       </c>
-      <c r="Q2">
-        <v>0</v>
-      </c>
       <c r="R2">
         <v>0</v>
       </c>
@@ -678,58 +729,58 @@
         <v>0</v>
       </c>
       <c r="T2">
-        <v>0.5555555555555555</v>
+        <v>1.111111111111111</v>
       </c>
       <c r="U2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W2" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X2">
-        <v>23.81</v>
+        <v>74.03</v>
       </c>
       <c r="Y2">
-        <v>43.42</v>
+        <v>117.78</v>
       </c>
       <c r="Z2">
-        <v>29.79</v>
+        <v>463.81</v>
       </c>
       <c r="AA2">
-        <v>146.73</v>
+        <v>8.109999999999999</v>
       </c>
       <c r="AB2">
-        <v>24.66</v>
+        <v>98.8</v>
       </c>
       <c r="AC2">
-        <v>13.33</v>
+        <v>141.41</v>
       </c>
       <c r="AD2">
-        <v>7.06</v>
+        <v>6.45</v>
       </c>
       <c r="AE2">
-        <v>-5.56</v>
+        <v>-33.97</v>
       </c>
       <c r="AF2">
-        <v>-1.37</v>
+        <v>11.16</v>
       </c>
       <c r="AG2">
-        <v>21.67</v>
+        <v>228.91</v>
       </c>
       <c r="AH2" t="s">
-        <v>39</v>
+        <v>44</v>
       </c>
       <c r="AI2" t="s">
-        <v>41</v>
+        <v>51</v>
       </c>
       <c r="AJ2" t="s">
-        <v>43</v>
+        <v>55</v>
       </c>
       <c r="AK2">
-        <v>55.00000000000001</v>
+        <v>84.29034981808027</v>
       </c>
     </row>
     <row r="3" spans="1:37">
@@ -737,40 +788,40 @@
         <v>38</v>
       </c>
       <c r="B3">
-        <v>94.17670682730925</v>
+        <v>95.78313253012048</v>
       </c>
       <c r="C3">
-        <v>73</v>
+        <v>59</v>
       </c>
       <c r="D3">
-        <v>45.98</v>
+        <v>53.84</v>
       </c>
       <c r="E3">
-        <v>1.3</v>
+        <v>2.07</v>
       </c>
       <c r="F3">
-        <v>-0.7071067811865475</v>
+        <v>-0.1510928461625242</v>
       </c>
       <c r="G3">
-        <v>3.28</v>
+        <v>2.31</v>
       </c>
       <c r="H3">
-        <v>0.7071067811865475</v>
+        <v>0.3014622824434254</v>
       </c>
       <c r="I3">
-        <v>45.45299911499023</v>
+        <v>53.63399963378906</v>
       </c>
       <c r="J3">
-        <v>46.84774971008301</v>
+        <v>55.90500011444092</v>
       </c>
       <c r="K3">
-        <v>45.39924980163574</v>
+        <v>53.48619995117188</v>
       </c>
       <c r="L3">
-        <v>38.67618746757508</v>
+        <v>44.36285002708435</v>
       </c>
       <c r="M3">
-        <v>0.97</v>
+        <v>0.96</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -779,7 +830,7 @@
         <v>5</v>
       </c>
       <c r="Q3">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="R3">
         <v>0</v>
@@ -788,58 +839,608 @@
         <v>0</v>
       </c>
       <c r="T3">
+        <v>6.111111111111111</v>
+      </c>
+      <c r="U3" t="b">
+        <v>0</v>
+      </c>
+      <c r="V3" t="b">
+        <v>0</v>
+      </c>
+      <c r="W3" t="b">
+        <v>0</v>
+      </c>
+      <c r="X3">
+        <v>30.65</v>
+      </c>
+      <c r="Y3">
+        <v>59.45</v>
+      </c>
+      <c r="Z3">
+        <v>76.81999999999999</v>
+      </c>
+      <c r="AA3">
+        <v>-99.18000000000001</v>
+      </c>
+      <c r="AB3">
+        <v>42.94</v>
+      </c>
+      <c r="AC3">
+        <v>108.33</v>
+      </c>
+      <c r="AD3">
+        <v>6.02</v>
+      </c>
+      <c r="AE3">
+        <v>17.19</v>
+      </c>
+      <c r="AF3">
+        <v>-5.88</v>
+      </c>
+      <c r="AG3">
+        <v>88.89</v>
+      </c>
+      <c r="AH3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AI3" t="s">
+        <v>51</v>
+      </c>
+      <c r="AJ3" t="s">
+        <v>56</v>
+      </c>
+      <c r="AK3">
+        <v>73.70714267931918</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37">
+      <c r="A4" t="s">
+        <v>39</v>
+      </c>
+      <c r="B4">
+        <v>96.18473895582329</v>
+      </c>
+      <c r="C4">
+        <v>446</v>
+      </c>
+      <c r="D4">
+        <v>450.02</v>
+      </c>
+      <c r="E4">
+        <v>2.69</v>
+      </c>
+      <c r="F4">
+        <v>0.5391628931483762</v>
+      </c>
+      <c r="G4">
+        <v>2.13</v>
+      </c>
+      <c r="H4">
+        <v>-0.09420696326357117</v>
+      </c>
+      <c r="I4">
+        <v>454.597998046875</v>
+      </c>
+      <c r="J4">
+        <v>420.6925003051758</v>
+      </c>
+      <c r="K4">
+        <v>383.6694012451172</v>
+      </c>
+      <c r="L4">
+        <v>316.4018504333496</v>
+      </c>
+      <c r="M4">
+        <v>1.08</v>
+      </c>
+      <c r="N4">
+        <v>1.18</v>
+      </c>
+      <c r="P4">
+        <v>0</v>
+      </c>
+      <c r="Q4">
+        <v>0</v>
+      </c>
+      <c r="R4">
+        <v>0</v>
+      </c>
+      <c r="S4">
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <v>1.666666666666667</v>
+      </c>
+      <c r="U4" t="b">
+        <v>0</v>
+      </c>
+      <c r="V4" t="b">
+        <v>1</v>
+      </c>
+      <c r="W4" t="b">
+        <v>1</v>
+      </c>
+      <c r="X4">
+        <v>230.54</v>
+      </c>
+      <c r="Y4">
+        <v>466.01</v>
+      </c>
+      <c r="Z4">
+        <v>25.23</v>
+      </c>
+      <c r="AA4">
+        <v>1.82</v>
+      </c>
+      <c r="AB4">
+        <v>22.97</v>
+      </c>
+      <c r="AC4">
+        <v>79.48999999999999</v>
+      </c>
+      <c r="AD4">
+        <v>9.050000000000001</v>
+      </c>
+      <c r="AE4">
+        <v>4.72</v>
+      </c>
+      <c r="AF4">
+        <v>25.76</v>
+      </c>
+      <c r="AG4">
+        <v>36.29</v>
+      </c>
+      <c r="AH4" t="s">
+        <v>46</v>
+      </c>
+      <c r="AI4" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ4" t="s">
+        <v>57</v>
+      </c>
+      <c r="AK4">
+        <v>51.53875556619819</v>
+      </c>
+    </row>
+    <row r="5" spans="1:37">
+      <c r="A5" t="s">
+        <v>40</v>
+      </c>
+      <c r="B5">
+        <v>96.3855421686747</v>
+      </c>
+      <c r="C5">
+        <v>193</v>
+      </c>
+      <c r="D5">
+        <v>70.13</v>
+      </c>
+      <c r="E5">
+        <v>1.03</v>
+      </c>
+      <c r="F5">
+        <v>-1.308941183071131</v>
+      </c>
+      <c r="G5">
+        <v>2.07</v>
+      </c>
+      <c r="H5">
+        <v>-0.22609671183257</v>
+      </c>
+      <c r="I5">
+        <v>69.4586669921875</v>
+      </c>
+      <c r="J5">
+        <v>70.06108245849609</v>
+      </c>
+      <c r="K5">
+        <v>66.76436630249023</v>
+      </c>
+      <c r="L5">
+        <v>54.90468326568603</v>
+      </c>
+      <c r="M5">
+        <v>0.99</v>
+      </c>
+      <c r="N5">
+        <v>1.04</v>
+      </c>
+      <c r="P5">
+        <v>3</v>
+      </c>
+      <c r="Q5">
+        <v>3</v>
+      </c>
+      <c r="R5">
+        <v>0</v>
+      </c>
+      <c r="S5">
+        <v>0</v>
+      </c>
+      <c r="T5">
         <v>5</v>
       </c>
-      <c r="U3" t="b">
+      <c r="U5" t="b">
         <v>1</v>
       </c>
-      <c r="V3" t="b">
+      <c r="V5" t="b">
+        <v>0</v>
+      </c>
+      <c r="W5" t="b">
+        <v>0</v>
+      </c>
+      <c r="X5">
+        <v>35.49</v>
+      </c>
+      <c r="Y5">
+        <v>72.22</v>
+      </c>
+      <c r="Z5">
+        <v>10.61</v>
+      </c>
+      <c r="AA5">
+        <v>230.42</v>
+      </c>
+      <c r="AB5">
+        <v>5.27</v>
+      </c>
+      <c r="AC5">
+        <v>318.64</v>
+      </c>
+      <c r="AD5">
+        <v>15.75</v>
+      </c>
+      <c r="AE5">
+        <v>175.47</v>
+      </c>
+      <c r="AF5">
+        <v>129.36</v>
+      </c>
+      <c r="AG5">
+        <v>-33.74</v>
+      </c>
+      <c r="AH5" t="s">
+        <v>47</v>
+      </c>
+      <c r="AI5" t="s">
+        <v>53</v>
+      </c>
+      <c r="AJ5" t="s">
+        <v>58</v>
+      </c>
+      <c r="AK5">
+        <v>43.18181818181818</v>
+      </c>
+    </row>
+    <row r="6" spans="1:37">
+      <c r="A6" t="s">
+        <v>41</v>
+      </c>
+      <c r="B6">
+        <v>93.57429718875501</v>
+      </c>
+      <c r="C6">
+        <v>41</v>
+      </c>
+      <c r="D6">
+        <v>84.75</v>
+      </c>
+      <c r="E6">
+        <v>3.25</v>
+      </c>
+      <c r="F6">
+        <v>1.162619689945318</v>
+      </c>
+      <c r="G6">
+        <v>3.06</v>
+      </c>
+      <c r="H6">
+        <v>1.95008413955591</v>
+      </c>
+      <c r="I6">
+        <v>83.03399963378907</v>
+      </c>
+      <c r="J6">
+        <v>73.58350009918213</v>
+      </c>
+      <c r="K6">
+        <v>69.25119972229004</v>
+      </c>
+      <c r="L6">
+        <v>64.08005002975464</v>
+      </c>
+      <c r="M6">
+        <v>1.13</v>
+      </c>
+      <c r="N6">
+        <v>1.2</v>
+      </c>
+      <c r="P6">
+        <v>0</v>
+      </c>
+      <c r="Q6">
+        <v>0</v>
+      </c>
+      <c r="R6">
+        <v>0</v>
+      </c>
+      <c r="S6">
+        <v>0</v>
+      </c>
+      <c r="T6">
+        <v>0</v>
+      </c>
+      <c r="U6" t="b">
+        <v>0</v>
+      </c>
+      <c r="V6" t="b">
         <v>1</v>
       </c>
-      <c r="W3" t="b">
-        <v>0</v>
-      </c>
-      <c r="X3">
-        <v>24.55</v>
-      </c>
-      <c r="Y3">
-        <v>49.67</v>
-      </c>
-      <c r="Z3">
-        <v>12.82</v>
-      </c>
-      <c r="AA3">
-        <v>61.24</v>
-      </c>
-      <c r="AB3">
-        <v>22.74</v>
-      </c>
-      <c r="AC3">
-        <v>37.07</v>
-      </c>
-      <c r="AD3">
-        <v>8.4</v>
-      </c>
-      <c r="AE3">
-        <v>11.97</v>
-      </c>
-      <c r="AF3">
-        <v>2.16</v>
-      </c>
-      <c r="AG3">
-        <v>19.83</v>
-      </c>
-      <c r="AH3" t="s">
-        <v>40</v>
-      </c>
-      <c r="AI3" t="s">
+      <c r="W6" t="b">
+        <v>0</v>
+      </c>
+      <c r="X6">
+        <v>44.76</v>
+      </c>
+      <c r="Y6">
+        <v>87.55</v>
+      </c>
+      <c r="Z6">
+        <v>27.95</v>
+      </c>
+      <c r="AA6">
+        <v>17.34</v>
+      </c>
+      <c r="AB6">
+        <v>22.28</v>
+      </c>
+      <c r="AC6">
+        <v>14.75</v>
+      </c>
+      <c r="AD6">
+        <v>9.74</v>
+      </c>
+      <c r="AE6">
+        <v>94.44</v>
+      </c>
+      <c r="AF6">
+        <v>-31.43</v>
+      </c>
+      <c r="AG6">
+        <v>-13.93</v>
+      </c>
+      <c r="AH6" t="s">
+        <v>48</v>
+      </c>
+      <c r="AI6" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ6" t="s">
+        <v>59</v>
+      </c>
+      <c r="AK6">
+        <v>33.04196610659108</v>
+      </c>
+    </row>
+    <row r="7" spans="1:37">
+      <c r="A7" t="s">
         <v>42</v>
       </c>
-      <c r="AJ3" t="s">
-        <v>44</v>
-      </c>
-      <c r="AK3">
-        <v>44.99999999999999</v>
+      <c r="B7">
+        <v>95.58232931726907</v>
+      </c>
+      <c r="C7">
+        <v>480</v>
+      </c>
+      <c r="D7">
+        <v>661.11</v>
+      </c>
+      <c r="E7">
+        <v>3.29</v>
+      </c>
+      <c r="F7">
+        <v>1.207152318287957</v>
+      </c>
+      <c r="G7">
+        <v>2.19</v>
+      </c>
+      <c r="H7">
+        <v>0.03768278530542769</v>
+      </c>
+      <c r="I7">
+        <v>670.6500122070313</v>
+      </c>
+      <c r="J7">
+        <v>600.8749938964844</v>
+      </c>
+      <c r="K7">
+        <v>583.7743994140625</v>
+      </c>
+      <c r="L7">
+        <v>535.4622497558594</v>
+      </c>
+      <c r="M7">
+        <v>1.12</v>
+      </c>
+      <c r="N7">
+        <v>1.15</v>
+      </c>
+      <c r="P7">
+        <v>0</v>
+      </c>
+      <c r="Q7">
+        <v>0</v>
+      </c>
+      <c r="R7">
+        <v>0</v>
+      </c>
+      <c r="S7">
+        <v>0</v>
+      </c>
+      <c r="T7">
+        <v>0</v>
+      </c>
+      <c r="U7" t="b">
+        <v>0</v>
+      </c>
+      <c r="V7" t="b">
+        <v>1</v>
+      </c>
+      <c r="W7" t="b">
+        <v>1</v>
+      </c>
+      <c r="X7">
+        <v>440.48</v>
+      </c>
+      <c r="Y7">
+        <v>685.23</v>
+      </c>
+      <c r="Z7">
+        <v>28.42</v>
+      </c>
+      <c r="AA7">
+        <v>3.01</v>
+      </c>
+      <c r="AB7">
+        <v>11.72</v>
+      </c>
+      <c r="AC7">
+        <v>6.61</v>
+      </c>
+      <c r="AD7">
+        <v>14.52</v>
+      </c>
+      <c r="AE7">
+        <v>-8.779999999999999</v>
+      </c>
+      <c r="AF7">
+        <v>15.1</v>
+      </c>
+      <c r="AG7">
+        <v>1.55</v>
+      </c>
+      <c r="AH7" t="s">
+        <v>49</v>
+      </c>
+      <c r="AI7" t="s">
+        <v>52</v>
+      </c>
+      <c r="AJ7" t="s">
+        <v>60</v>
+      </c>
+      <c r="AK7">
+        <v>14.2569217118677</v>
+      </c>
+    </row>
+    <row r="8" spans="1:37">
+      <c r="A8" t="s">
+        <v>43</v>
+      </c>
+      <c r="B8">
+        <v>94.97991967871486</v>
+      </c>
+      <c r="C8">
+        <v>313</v>
+      </c>
+      <c r="D8">
+        <v>81.63</v>
+      </c>
+      <c r="E8">
+        <v>1.34</v>
+      </c>
+      <c r="F8">
+        <v>-0.9638133134156807</v>
+      </c>
+      <c r="G8">
+        <v>1.83</v>
+      </c>
+      <c r="H8">
+        <v>-0.7536557061085645</v>
+      </c>
+      <c r="I8">
+        <v>82.46399993896485</v>
+      </c>
+      <c r="J8">
+        <v>79.70249977111817</v>
+      </c>
+      <c r="K8">
+        <v>73.87779998779297</v>
+      </c>
+      <c r="L8">
+        <v>63.10719995498657</v>
+      </c>
+      <c r="M8">
+        <v>1.03</v>
+      </c>
+      <c r="N8">
+        <v>1.12</v>
+      </c>
+      <c r="P8">
+        <v>0</v>
+      </c>
+      <c r="Q8">
+        <v>0</v>
+      </c>
+      <c r="R8">
+        <v>0</v>
+      </c>
+      <c r="S8">
+        <v>0</v>
+      </c>
+      <c r="T8">
+        <v>0</v>
+      </c>
+      <c r="U8" t="b">
+        <v>0</v>
+      </c>
+      <c r="V8" t="b">
+        <v>1</v>
+      </c>
+      <c r="W8" t="b">
+        <v>0</v>
+      </c>
+      <c r="X8">
+        <v>48.8</v>
+      </c>
+      <c r="Y8">
+        <v>83.66</v>
+      </c>
+      <c r="Z8">
+        <v>9.960000000000001</v>
+      </c>
+      <c r="AA8">
+        <v>219.69</v>
+      </c>
+      <c r="AB8">
+        <v>6.68</v>
+      </c>
+      <c r="AC8">
+        <v>6.45</v>
+      </c>
+      <c r="AD8">
+        <v>8.81</v>
+      </c>
+      <c r="AE8">
+        <v>-27.63</v>
+      </c>
+      <c r="AF8">
+        <v>47.1</v>
+      </c>
+      <c r="AG8">
+        <v>0</v>
+      </c>
+      <c r="AH8" t="s">
+        <v>50</v>
+      </c>
+      <c r="AI8" t="s">
+        <v>54</v>
+      </c>
+      <c r="AJ8" t="s">
+        <v>61</v>
+      </c>
+      <c r="AK8">
+        <v>4.031368262607984</v>
       </c>
     </row>
   </sheetData>
